--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,200 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128862500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92164</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>898</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>522080</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7035884</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128862495</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522048</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7035938</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92199</v>
+        <v>92206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92230</v>
+        <v>92231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862500</v>
       </c>
       <c r="B3" t="n">
-        <v>92231</v>
+        <v>92234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128862495</v>
       </c>
       <c r="B4" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046664</v>
+        <v>89046662</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522526.9440600761</v>
+        <v>522514</v>
       </c>
       <c r="R2" t="n">
-        <v>7035815.842271592</v>
+        <v>7035888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>kant av fuktdråg med medelålders gran</t>
+          <t>gammal kalkgranskog i örtrik moränsvacka intill lok</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,45 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128862500</v>
+        <v>89046664</v>
       </c>
       <c r="B3" t="n">
-        <v>92234</v>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Ruvens östsida, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522080</v>
+        <v>522527</v>
       </c>
       <c r="R3" t="n">
-        <v>7035884</v>
+        <v>7035816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,61 +862,70 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kant av fuktdråg med medelålders gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128862495</v>
+        <v>89046668</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Ruvens östsida, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522048</v>
+        <v>522346</v>
       </c>
       <c r="R4" t="n">
-        <v>7035938</v>
+        <v>7035942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +968,456 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre kalkgranskog i örtrik moränsvacka intill lok</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128862500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92605</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>898</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522080</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7035884</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128862495</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522048</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7035938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89046663</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97518</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mikroskapania</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scapania carinthiaca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>J.B.Jack ex Lindb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522512</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7035879</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>i mindre lok med gyttjig botten</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tidvis dränkt gammal låga</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89046657</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522476</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7035920</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>på liten ö i lok med kalkpåverkad barrnaturskog runt</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2 substratenheter # gamla flerstammiga sälgar på socklar</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33325-2025 artfynd.xlsx
+++ b/artfynd/A 33325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046663</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>